--- a/AAII_Financials/Quarterly/TELNY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TELNY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="92">
   <si>
     <t>TELNY</t>
   </si>
@@ -656,177 +656,181 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -869,86 +873,89 @@
       <c r="P8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R8" s="3">
         <v>1849500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1847400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2659500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2562100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1417100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2515000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2550100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2583900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2483500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3039500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3219500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3236500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3165100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3421100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3112400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3010000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2674300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2820000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2813600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2777400</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2247000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>3179900</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>3280600</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>3402600</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>15461200</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>3853000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -991,86 +998,89 @@
       <c r="P9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R9" s="3">
         <v>458300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>406600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>696700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>680400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>426600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>628700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>647300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>686400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>780400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>702800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>780300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>795900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>785200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>816200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>725100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>700800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>588400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>619800</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>662700</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>632900</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>523300</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>725500</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>760900</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>1192600</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>5577700</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>1329500</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1113,86 +1123,89 @@
       <c r="P10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R10" s="3">
         <v>1391200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1440800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1962700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1881600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>990500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1886300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1902900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1897500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1703200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2336700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2439200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2440500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2380000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2605000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>2387300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2309300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>2085900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>2200200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>2150900</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>2144500</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1723800</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>2454400</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>2519700</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>2210000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>9883500</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>2523500</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1235,8 +1248,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1357,8 +1371,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1479,8 +1496,11 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1523,86 +1543,89 @@
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="3">
         <v>32100</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>10500</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>259800</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>16900</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>93600</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>16900</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>13700</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>10300</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>15300</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>10900</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>147800</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>37000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>37100</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>5200</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>26900</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>20700</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>268700</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>25500</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>26600</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>18600</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>59900</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>55600</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>718100</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>-82400</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>158900</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>707900</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1645,86 +1668,89 @@
       <c r="P15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="Q15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R15" s="3">
         <v>410300</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>394500</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>622000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>603300</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>360100</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>607100</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>603000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>599100</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>459400</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>722500</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>761100</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>722000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>756200</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>757100</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>666800</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>637800</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>462800</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>553400</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>529200</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>547800</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>457600</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>556300</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>570100</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>581900</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>2414600</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>617700</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,8 +1790,9 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1808,86 +1835,89 @@
       <c r="P17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R17" s="3">
         <v>1543100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1376400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2368500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1912500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1395100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1956000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2017600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2050200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1679400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2209800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2664400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2547000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2550200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2612300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2398400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2269400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2378100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2132300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2221000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2183200</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1893900</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>2354800</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>3111300</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>2705400</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>12375000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>3663500</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1930,86 +1960,89 @@
       <c r="P18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R18" s="3">
         <v>306400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>471100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>291000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>649600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>22000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>558900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>532500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>533700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>804100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>829700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>555100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>689500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>614900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>808800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>714000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>740600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>296200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>687700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>592500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>594300</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>353200</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>825100</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>169300</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>697100</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>3086200</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>189500</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2052,8 +2085,9 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2096,86 +2130,89 @@
       <c r="P20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R20" s="3">
         <v>90500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-228500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-211300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>15700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-9600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-86700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-59500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>19500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>219500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>49700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>120200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-404300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>85200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-202000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>7100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>62800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-258100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>9800</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-124000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>233900</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-45200</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>211800</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>102900</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>100400</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-323500</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>90900</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2218,86 +2255,89 @@
       <c r="P21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R21" s="3">
         <v>995100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>851500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>938900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1268700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>712400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1083600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1108000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1820400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1768500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1602000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1517400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1080600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1464700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1363200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1387700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1445100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>516500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1252700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1017600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1422600</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1009200</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1647600</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>934400</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>1428400</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>6219100</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>1416700</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2340,86 +2380,89 @@
       <c r="P22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="Q22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R22" s="3">
         <v>123300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>43700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>58700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>45200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>48700</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>61000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>61600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>60700</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>110900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>107400</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>85400</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>89800</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>173900</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>135400</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>117100</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>100900</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>104900</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>45900</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>46200</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>30500</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>105800</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>54700</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>72700</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>72500</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>382700</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>69500</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2462,86 +2505,89 @@
       <c r="P23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R23" s="3">
         <v>273600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>198800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>21100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>620100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-36300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>411200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>411400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>492600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>912600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>772100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>589800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>195400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>526300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>471500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>603900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>702600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-66900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>651500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>422300</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>797600</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>202200</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>982200</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>199500</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>725000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>2379900</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>210800</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2584,86 +2630,89 @@
       <c r="P24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R24" s="3">
         <v>-166900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>78100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-36300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-100500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>39800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>134300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>138100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>154900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>158700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>217500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>221300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>69100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>147500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>483800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>216100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>203000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>55800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>205700</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>125000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>235000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>77200</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>272900</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>186400</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>197900</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>730400</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>202600</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,8 +2833,11 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2828,86 +2880,89 @@
       <c r="P26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R26" s="3">
         <v>440500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>120700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>57400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>720600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-76100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>276900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>273200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>337700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>754000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>554600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>368500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>126300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>378700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-12400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>387800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>499600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-122700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>445800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>297300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>562700</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>124900</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>709300</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>13100</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>527100</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>1649500</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>8300</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2950,86 +3005,89 @@
       <c r="P27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R27" s="3">
         <v>399500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>47500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-16100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>656000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-142100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>203200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>197800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>266500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>668600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>461100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>266200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>9600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>277900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-113600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>302100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>397100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-160200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>370200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>208100</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>484100</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>46100</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>623500</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>-79500</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>441500</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>1282600</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>-93500</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3194,86 +3255,89 @@
       <c r="P29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="Q29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R29" s="3">
         <v>3165300</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>99000</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-89500</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-32700</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>147100</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>39200</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>7600</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-631800</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>127800</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>225600</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>67900</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>-86600</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>31900</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>28000</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>35400</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>297100</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>231400</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>62500</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>26600</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>211500</v>
       </c>
-      <c r="AL29" s="3">
+      <c r="AM29" s="3">
         <v>42800</v>
       </c>
-      <c r="AM29" s="3">
+      <c r="AN29" s="3">
         <v>60200</v>
       </c>
-      <c r="AN29" s="3">
+      <c r="AO29" s="3">
         <v>72400</v>
       </c>
-      <c r="AO29" s="3">
+      <c r="AP29" s="3">
         <v>-933600</v>
       </c>
-      <c r="AP29" s="3">
+      <c r="AQ29" s="3">
         <v>-501000</v>
       </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,8 +3583,11 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3560,86 +3630,89 @@
       <c r="P32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R32" s="3">
         <v>-90500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>228500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>211300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-15700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>9600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>86700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>59500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-19500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-219500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-49700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-120200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>404300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-85200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>202000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-7100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-62800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>258100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-9800</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>124000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-233900</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>45200</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-211800</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-102900</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-100400</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>323500</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-90900</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3682,86 +3755,89 @@
       <c r="P33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="Q33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R33" s="3">
         <v>3564800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>146500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-105600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>623200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>5000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>242400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>205500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-365300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>796400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>458600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>491800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>77400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>191400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-81700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>330100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>432600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>136900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>601600</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>270600</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>510700</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>257600</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>666400</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>-19300</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>513900</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>348900</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>-594400</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,8 +3958,11 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3926,213 +4005,219 @@
       <c r="P35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="Q35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R35" s="3">
         <v>3564800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>146500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-105600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>623200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>5000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>242400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>205500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-365300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>796400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>458600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>491800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>77400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>191400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-81700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>330100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>432600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>136900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>601600</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>270600</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>510700</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>257600</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>666400</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>-19300</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>513900</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>348900</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>-594400</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,130 +4305,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3200000</v>
+      </c>
+      <c r="E41" s="3">
         <v>4889200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1620400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1055500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>614900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>921700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>913700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1582900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1306100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1926200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1928500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>910500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1168300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1371900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>933700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1534600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>892800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1972900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1431900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2018200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1852900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2139500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2131400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1771000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1855300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2006900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1534800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>3841300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>4899600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1569900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2086300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>3345800</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1900500</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>2144100</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>2610600</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>3448500</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>2389300</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>3222400</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>2846400</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>3399800</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4350,11 +4440,11 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>44600</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
         <v>0</v>
       </c>
@@ -4362,963 +4452,987 @@
         <v>0</v>
       </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>35300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>135700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>245900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>125400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>32200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>30400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>30300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>31300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>33900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>69500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>57500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>62000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>78900</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>93000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>71500</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>54300</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>59700</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>54500</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>65400</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>93700</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>100700</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>80600</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>97200</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>103000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>76500</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>93200</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>83200</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>69000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>187800</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>189300</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>192000</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>297900</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>306900</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>261000</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1254200</v>
+      </c>
+      <c r="E43" s="3">
         <v>1291500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1145900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1370300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1354900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1277300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1143800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1343400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1375500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1380000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1453000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1393300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1453400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1568500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1771900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2146100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2167600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2025600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2044800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2132100</v>
-      </c>
-      <c r="W43" s="3">
-        <v>2213800</v>
       </c>
       <c r="X43" s="3">
         <v>2213800</v>
       </c>
       <c r="Y43" s="3">
+        <v>2213800</v>
+      </c>
+      <c r="Z43" s="3">
         <v>2730300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2652100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2945000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>3052900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>3000200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>3410000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2509600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>3068800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2537200</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2310300</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>2155700</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>2118400</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>2990300</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>2713200</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>2991200</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>3085500</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>3158100</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>2854000</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>100500</v>
+      </c>
+      <c r="E44" s="3">
         <v>86900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>85500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>90500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>91300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>83400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>77200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>83700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>82000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>94500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>94200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>99800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>116300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>122700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>146600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>174000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>158600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>148200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>147000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>103400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>121500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>149300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>136000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>127100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>142500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>172600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>164400</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>163400</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>133400</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>168100</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>192100</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>101800</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>115000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>149800</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>205300</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>174100</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>200000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>210800</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>222200</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>175900</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>943300</v>
+      </c>
+      <c r="E45" s="3">
         <v>969600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>48000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>200400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>122100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>139100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>23500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>38300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>45400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>56500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>209600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>46400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>47300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>25000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>140200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>141300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>154900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>140900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>421300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>417800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>385700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>143600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>128400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>141200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>187400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>599400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>386200</v>
       </c>
-      <c r="AD45" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF45" s="3">
+      <c r="AE45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG45" s="3">
         <v>395000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>101800</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>439600</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>2973600</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>3045100</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>197100</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>178000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>117900</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>438000</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>200</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5521600</v>
+      </c>
+      <c r="E46" s="3">
         <v>7255400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3167800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2802900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2285800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2503000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2416500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3234800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3103800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3640400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3920600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2565300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2885200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3171000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3026400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>4065600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3431500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>4349600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>4123900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>4764600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4645400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>4700400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>5185700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>4746000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>5195700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>5925500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>5186200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>7495400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>7639800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>5304800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>4993900</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>6290700</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>7227900</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>7526400</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>6191100</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>6703100</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>5890400</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>7254600</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>6533800</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>6691100</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>3168000</v>
+      </c>
+      <c r="E47" s="3">
         <v>3200600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>7189600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>6409900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>6516500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>5951400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>6369800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>6414000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>5474200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>5489700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>5518400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>5724600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>5865500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>5749600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>3732100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>576900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>558400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>532200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>534500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>533300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>565300</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>587200</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>664700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>826000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>847800</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>543800</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>475800</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>272000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>253700</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>486700</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>268700</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>52000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>53500</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>53300</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>55600</v>
-      </c>
-      <c r="AL47" s="3">
-        <v>51200</v>
       </c>
       <c r="AM47" s="3">
         <v>51200</v>
       </c>
       <c r="AN47" s="3">
+        <v>51200</v>
+      </c>
+      <c r="AO47" s="3">
         <v>1738500</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>1944800</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>1690700</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7186900</v>
+      </c>
+      <c r="E48" s="3">
         <v>7255200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>7130300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>7720700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>7700800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>7445300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>7112000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>7471100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>7340700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>7417400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>7639000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>7465400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>7587900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>7683400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>10470900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>11988200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>11906500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>11630300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>11694700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>11352200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>11879500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>11961800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>14727000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>14716600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>16542600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>17296600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>15778500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>16995100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>14544500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>16139200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>8276600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>7060600</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>7104000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>6984200</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>8748700</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>8271800</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>8497000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>9027500</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>8879600</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>8405100</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3475000</v>
+      </c>
+      <c r="E49" s="3">
         <v>3529000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3591100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3571700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3578200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3333200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3156500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3393000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3271200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3293200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3403300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3227700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3334400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3352000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3481600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3674300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>3603500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>3422500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>3540700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3501700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3610100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3575500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>4160700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>4237300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>4643000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>4839800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>4296700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>5123000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>2361900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>4394900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>5728300</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>3698000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>3864400</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>4002500</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>6605500</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>6627500</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>6847600</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>6962500</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>7099100</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>7250400</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,130 +5678,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1244200</v>
+      </c>
+      <c r="E52" s="3">
         <v>1202900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>27000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1215700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1181900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1220300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>116100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1233800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1198500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1346200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>95800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1612000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1628600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1912600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1788000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1789400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1772500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1564500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1339300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1285100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1453900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1509100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1833200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1877000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>2144700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>2457300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1810800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>2484200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>2288400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1852300</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>2311800</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1982900</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1485500</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1533000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>1761500</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>1790700</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>2147400</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>850000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>981800</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>874400</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>20792700</v>
+      </c>
+      <c r="E54" s="3">
         <v>22751400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>21987700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>22172000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>21680900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>20864300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>20140000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>22066300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>20703500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>21577000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>21535400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>20953700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>21761100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>22376200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>22499000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>22094300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>21272400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>21499100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>21233100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>21436900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>22154100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>22334000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>26571300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>26402800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>29373700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>31063100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>27548100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>32369600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>27088300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>28177900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>21579300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>19084400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>19735400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>20099400</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>23362400</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>23444200</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>23433600</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>25833200</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>25439100</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>24911800</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,740 +6145,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1972200</v>
+      </c>
+      <c r="E57" s="3">
         <v>2069000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>646000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2163900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2114900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2109600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>584100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2025300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2059400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2031600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>542500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1946100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2019500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2104300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2654500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2980200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2954800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2927300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3040000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2817800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2822500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2982600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>3510400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>3344800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>3834100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>4089800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>3950300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>4383300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>3795600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>4040600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>4256500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>3576100</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>3484800</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>3486000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>4665800</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>4258800</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>4539200</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>4887000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>5288300</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>4924500</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>446700</v>
+      </c>
+      <c r="E58" s="3">
         <v>1552000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1613700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1732900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1670800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1073800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1337400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2118600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2025300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1380400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1620600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>939500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1613400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1422800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1489900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1679300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1238600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1486400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1528800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1664800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2078100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1462000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1718800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1883200</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>2466100</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>2069500</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>2662500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>4165700</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>3453100</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>2723400</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1775800</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1588700</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>2615700</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>2051000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>2629600</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>2984700</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>3083000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>4001300</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>3202100</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>3174000</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1760000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1000900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1339600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1453800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1412700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>824000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1158800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1292100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1273100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>745100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1299300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1318200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1275000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>830400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>912800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1683400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1622000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1133200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1278700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1728800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1762500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1005200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1041100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1639300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1928100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1480500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1470400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2325000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2159400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1504100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1578100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2654800</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2280400</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1900000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1583800</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>2214000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>2207700</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>1558500</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>1079900</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>1033600</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4178800</v>
+      </c>
+      <c r="E60" s="3">
         <v>4621900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4591500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5350600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5198400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4007400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4082800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>5436000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5357900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4157100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4535400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4203800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4908000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4357500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>5057200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>6342800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>5815400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>5546800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>5847400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>6211400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>6663100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>5449900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>6270300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>6867300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>8228300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>7639800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>8083200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>10873900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>9408000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>8268000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>7610400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>7819600</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>8380900</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>7437000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>8879100</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>9457500</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>9829900</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>10446800</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>9570300</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>9132100</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>8360900</v>
+      </c>
+      <c r="E61" s="3">
         <v>8414700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>8490100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>8230500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>8217800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>7975200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>7607400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>7830100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>7509900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>8333300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>8765700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>8055600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>8287200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>7990300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>10075500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>11255800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>11328000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>10733700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>10902700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>10874900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>11236200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>11596800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>13901600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>13888300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>15270500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>15872400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>12837700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>14534900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>11137800</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>13131100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>6309600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>4548900</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>4739300</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>4852400</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>5973300</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>5762600</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>5949300</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>6540000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>7446200</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>7214000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>790700</v>
+      </c>
+      <c r="E62" s="3">
         <v>804500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>767000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>772600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>776400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>775000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>729100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>723500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>714600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>724400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>775600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>714300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>724700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>799100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1312400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1686600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1562100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1481200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1520100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1510500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1560100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1579800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1850400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1790500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2093100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>2227800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1830500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1962200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1408000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1872300</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1515700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1260900</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>1244500</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>1065200</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>1292200</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>1284700</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>1223900</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>1479700</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>1592300</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>1503800</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>13919600</v>
+      </c>
+      <c r="E66" s="3">
         <v>14437000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>14485300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>14973200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>14778100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>13293400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>12942300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>14468700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>14040700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>13703200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>14589500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>13445800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>14395700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>13641900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>16843600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>19755200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>19206700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>18282800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>18759900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>19035000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>19933600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>19135300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>22601700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>23108300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>26282800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>26436000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>23336400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>27950500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>22521100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>23869900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>16000800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>14120200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>14910200</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>13911100</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>16704900</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>17006400</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>17551000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>19074800</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>19165800</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>18363900</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,130 +7938,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>8156300</v>
+      </c>
+      <c r="E72" s="3">
         <v>9398100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>8265800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>8534000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>8126500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>8709200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>7871400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>8400900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7993300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>8839200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>8301100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>8613400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>8340700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>9713600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>5180800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>1730200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>1549800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2847700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2111700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2030300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1803800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2791900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>3421800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>2516200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>2252700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>3551600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>3562800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>3647400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>3964700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>5195400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>4828000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>4471800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>4521900</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>5777800</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>6005900</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>5929300</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>5278900</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>5612000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>5136300</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>5466800</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6358000</v>
+      </c>
+      <c r="E76" s="3">
         <v>7779400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6991500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6707600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>6383000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7017800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>6676900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7081800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6088800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7259700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>6359100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>6962400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>6840500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>8201600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>5655400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2339100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2065800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3216200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2473200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2401900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2220500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>3198700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>3969600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>3294600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>3090900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>4627100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>4211700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>4419100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>4567200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>4308000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>5578500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>4964200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>4825200</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>6188300</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>6657500</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>6437800</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>5882600</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>6758400</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>6273400</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>6547800</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,135 +8688,141 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -8670,86 +8865,89 @@
       <c r="P81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="Q81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R81" s="3">
         <v>3564800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>146500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-105600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>623200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>5000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>242400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>205500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-365300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>796400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>458600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>491800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>77400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>191400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-81700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>330100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>432600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>136900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>601600</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>270600</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>510700</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>257600</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>666400</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>-19300</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>513900</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>348900</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>-594400</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,130 +8990,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>427700</v>
+      </c>
+      <c r="E83" s="3">
         <v>408400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>39100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>399900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>394500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>383700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>43800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>385200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>393600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>476400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>-454700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>594700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>663700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>726200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>598300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>609000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>859100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>603300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>700000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>611300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>635000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>1267200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>744900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>722500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>842100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>795400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>764600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>756300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>666600</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>641700</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>437000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>571000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>567700</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>597600</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>701200</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>610700</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>662200</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>630900</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>3456500</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>1136300</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>573100</v>
+      </c>
+      <c r="E89" s="3">
         <v>594800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>861100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>839800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>645800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>724500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>712600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>686200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>708100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>795300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>879700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>788100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>531100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>583400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>880800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1026700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>909600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>893000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>801700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1199300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>924400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1017300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1171000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1106800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1246300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1152100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>774300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1405400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>703500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1071600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>926100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1107200</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>895600</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>880500</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1064600</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>1399400</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>1343300</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>1129900</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>4904600</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>1293700</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,130 +9910,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-232100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-271000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-284000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-259000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-278400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-286000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-305000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-253300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-279300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-352800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-312600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-299200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-336200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-455400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-9177000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4428000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-5665000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-4491000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-4936000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-4134000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-439000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-535400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-504100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1395900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>571200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-610400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-8600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>1000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>32500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-101800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-827500</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-1315200</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>484600</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-568500</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-523100</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-449500</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-530800</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-1393000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-2925500</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-500200</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-217000</v>
+      </c>
+      <c r="E94" s="3">
         <v>2820800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-65400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-266300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-343800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-289100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-324900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-271100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-291300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-169400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-250200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-297600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-358500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-835800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1082500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-289100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-521000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-292700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-469500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-266300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-433500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-443000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>252400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-349300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-562400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-499100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1439700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-2515000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-535700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-564800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-906400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>1771500</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-448800</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-563600</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-511600</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-41700</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>50900</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-662400</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-2602200</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>93700</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,130 +10455,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E96" s="3">
+      <c r="D96" s="3">
+        <v>657300</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3">
         <v>624400</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>33500</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>643100</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I96" s="3">
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3">
         <v>541900</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K96" s="3">
+      <c r="K96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L96" s="3">
         <v>649800</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M96" s="3">
+      <c r="M96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N96" s="3">
         <v>601000</v>
       </c>
-      <c r="N96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O96" s="3">
+      <c r="O96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P96" s="3">
         <v>645800</v>
       </c>
-      <c r="P96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q96" s="3">
+      <c r="Q96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R96" s="3">
         <v>-565900</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-663700</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-526500</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-23400</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-633100</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-623200</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-695500</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-631400</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-741900</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-1368800</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
       <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-639200</v>
       </c>
-      <c r="AJ96" s="3">
-        <v>0</v>
-      </c>
       <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-606500</v>
       </c>
-      <c r="AL96" s="3">
-        <v>0</v>
-      </c>
       <c r="AM96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN96" s="3">
         <v>-747500</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-30800</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-1386600</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-32100</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,370 +10953,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1916200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-159800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-190800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-131700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-667900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-495100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-947700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-126900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1074700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-538900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>393000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-765400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-383900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>646200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-368600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-174300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1472900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-255600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-933400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-636000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-726000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-311400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1074200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-653300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-893600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-302200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1248800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-253200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>1835400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>209000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1683300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-1548700</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-652600</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-311900</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-1372300</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-107900</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-1948200</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-15300</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-1114300</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>503100</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E101" s="3">
         <v>-200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>3400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-8900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-14500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>12200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>1500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>14000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>42100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-25800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>71300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>22300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-16100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-23900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>73200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>21000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-13400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>19600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-37400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>20100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-24300</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-26100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-37000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-38800</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>154000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>10400</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>93000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-22000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-4100</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>10700</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-3400</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-5900</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-29500</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>72600</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-60200</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>15500</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>26300</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-55000</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>-70700</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1596300</v>
+      </c>
+      <c r="E102" s="3">
         <v>3217000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>597600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>436200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-355600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-59800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-556600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>279300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-672400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>99200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1023900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-274300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-197300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>435900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-594200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>636500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1063300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>331300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-581600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>259600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-215000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>238600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>323100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>67300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-248400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>504800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-1900700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-1268800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>1989000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>700100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-1652800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>1326600</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-211700</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-24400</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-864300</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>1083000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-642900</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>373700</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>1133100</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>1819800</v>
       </c>
     </row>
